--- a/Data/Home/Balcony.Temperature.xlsx
+++ b/Data/Home/Balcony.Temperature.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H147"/>
+  <dimension ref="A1:I157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>actionSource</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>violationLabel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,7 +492,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1709236460</v>
+        <v>1711833635</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -501,6 +506,7 @@
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -519,7 +525,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1709263589</v>
+        <v>1711863144</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -533,6 +539,7 @@
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -551,7 +558,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1709272142</v>
+        <v>1711871525</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -565,6 +572,7 @@
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -583,7 +591,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1709291610</v>
+        <v>1711899054</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -597,6 +605,7 @@
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -615,7 +624,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1709230981</v>
+        <v>1711915105</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -629,6 +638,7 @@
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -647,7 +657,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1709245049</v>
+        <v>1711942188</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -661,6 +671,7 @@
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -679,7 +690,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1709256234</v>
+        <v>1711950751</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -693,6 +704,7 @@
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -711,7 +723,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1709282723</v>
+        <v>1711961653</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -721,10 +733,11 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Balcony.Temperature.state: Comfortable</t>
+          <t>Balcony.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -743,7 +756,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1709321227</v>
+        <v>1711976047</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -753,10 +766,11 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Balcony.Temperature.state: Cold</t>
+          <t>Balcony.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -775,7 +789,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1709336634</v>
+        <v>1711984487</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -789,6 +803,7 @@
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -807,7 +822,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1709347445</v>
+        <v>1712000788</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -817,10 +832,11 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Balcony.Temperature.state: Warm</t>
+          <t>Balcony.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -839,7 +855,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1709371340</v>
+        <v>1712028780</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -853,6 +869,7 @@
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -871,7 +888,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1709436474</v>
+        <v>1712037343</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -885,6 +902,7 @@
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -903,7 +921,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1709485067</v>
+        <v>1712047402</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -913,10 +931,11 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Balcony.Temperature.state: Comfortable</t>
+          <t>Balcony.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -935,7 +954,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1709516745</v>
+        <v>1712060630</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -949,6 +968,7 @@
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -967,7 +987,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1709529387</v>
+        <v>1712074419</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -977,10 +997,11 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Balcony.Temperature.state: ExcessivelyHot</t>
+          <t>Balcony.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -999,7 +1020,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1709538523</v>
+        <v>1712086638</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1009,10 +1030,11 @@
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Balcony.Temperature.state: Warm</t>
+          <t>Balcony.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1031,7 +1053,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1709545521</v>
+        <v>1712114633</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1045,6 +1067,7 @@
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1063,7 +1086,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1709606285</v>
+        <v>1712123335</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1077,6 +1100,7 @@
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1095,7 +1119,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1709633011</v>
+        <v>1712133246</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1105,10 +1129,11 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Balcony.Temperature.state: Comfortable</t>
+          <t>Balcony.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1127,7 +1152,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1709666186</v>
+        <v>1712146421</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1137,10 +1162,11 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Balcony.Temperature.state: Cold</t>
+          <t>Balcony.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1159,7 +1185,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1709679073</v>
+        <v>1712154771</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1173,6 +1199,7 @@
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1191,7 +1218,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1709692089</v>
+        <v>1712172467</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1201,10 +1228,11 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Balcony.Temperature.state: Warm</t>
+          <t>Balcony.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1223,7 +1251,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1709715675</v>
+        <v>1712200241</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1237,6 +1265,7 @@
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1255,7 +1284,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1709744921</v>
+        <v>1712208659</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1265,10 +1294,11 @@
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Balcony.Temperature.state: Cold</t>
+          <t>Balcony.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1287,7 +1317,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1709766969</v>
+        <v>1712217788</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1297,10 +1327,11 @@
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Balcony.Temperature.state: Comfortable</t>
+          <t>Balcony.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1319,7 +1350,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1709777266</v>
+        <v>1712232418</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1333,6 +1364,7 @@
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1351,7 +1383,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1709804608</v>
+        <v>1712247581</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1365,6 +1397,7 @@
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1383,7 +1416,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1709866646</v>
+        <v>1712259840</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1393,10 +1426,11 @@
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Balcony.Temperature.state: Warm</t>
+          <t>Balcony.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1415,7 +1449,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1709886180</v>
+        <v>1712287264</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1429,6 +1463,7 @@
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1447,7 +1482,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1709927227</v>
+        <v>1712295807</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1457,10 +1492,11 @@
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Balcony.Temperature.state: Cold</t>
+          <t>Balcony.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1479,7 +1515,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1709937700</v>
+        <v>1712306419</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1489,10 +1525,11 @@
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Balcony.Temperature.state: Comfortable</t>
+          <t>Balcony.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1511,7 +1548,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1709949282</v>
+        <v>1712322022</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1525,6 +1562,7 @@
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1543,7 +1581,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1709980742</v>
+        <v>1712335839</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1557,6 +1595,7 @@
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1575,7 +1614,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1710007797</v>
+        <v>1712351995</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1589,6 +1628,7 @@
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1607,7 +1647,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1710021551</v>
+        <v>1712379984</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1621,6 +1661,7 @@
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1639,7 +1680,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1710033685</v>
+        <v>1712388467</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1653,6 +1694,7 @@
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1671,7 +1713,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1710062306</v>
+        <v>1712413429</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1685,6 +1727,7 @@
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1703,7 +1746,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1710124960</v>
+        <v>1712432727</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1713,10 +1756,11 @@
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Balcony.Temperature.state: Warm</t>
+          <t>Balcony.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1735,7 +1779,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1710154941</v>
+        <v>1712460619</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1749,6 +1793,7 @@
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1767,7 +1812,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1710225761</v>
+        <v>1712468954</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1781,6 +1826,7 @@
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1799,7 +1845,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1710236820</v>
+        <v>1712479813</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1809,10 +1855,11 @@
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Balcony.Temperature.state: Comfortable</t>
+          <t>Balcony.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1831,7 +1878,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1710270109</v>
+        <v>1712494149</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1841,10 +1888,11 @@
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Balcony.Temperature.state: Cold</t>
+          <t>Balcony.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1863,7 +1911,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1710280350</v>
+        <v>1712502656</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1877,6 +1925,7 @@
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1895,7 +1944,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1710300354</v>
+        <v>1712524458</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1905,10 +1954,11 @@
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Balcony.Temperature.state: Warm</t>
+          <t>Balcony.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1927,7 +1977,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1710321013</v>
+        <v>1712551958</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1941,6 +1991,7 @@
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1959,7 +2010,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1710348363</v>
+        <v>1712560666</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1969,10 +2020,11 @@
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Balcony.Temperature.state: Cold</t>
+          <t>Balcony.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1991,7 +2043,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1710368035</v>
+        <v>1712584673</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2005,6 +2057,7 @@
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2023,7 +2076,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1710383031</v>
+        <v>1712604732</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2033,10 +2086,11 @@
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Balcony.Temperature.state: Warm</t>
+          <t>Balcony.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2055,7 +2109,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1710403155</v>
+        <v>1712632570</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2069,6 +2123,7 @@
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2087,7 +2142,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1710438703</v>
+        <v>1712640982</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2097,10 +2152,11 @@
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Balcony.Temperature.state: Cold</t>
+          <t>Balcony.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2119,7 +2175,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1710456801</v>
+        <v>1712650614</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2129,10 +2185,11 @@
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Balcony.Temperature.state: Comfortable</t>
+          <t>Balcony.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2151,7 +2208,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1710469465</v>
+        <v>1712667035</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2165,6 +2222,7 @@
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2183,7 +2241,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1710479273</v>
+        <v>1712681304</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2193,10 +2251,11 @@
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Balcony.Temperature.state: ExcessivelyHot</t>
+          <t>Balcony.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2215,7 +2274,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1710488276</v>
+        <v>1712691516</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2225,10 +2284,11 @@
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Balcony.Temperature.state: Warm</t>
+          <t>Balcony.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2247,7 +2307,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1710495945</v>
+        <v>1712719370</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2261,6 +2321,7 @@
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2279,7 +2340,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1710533434</v>
+        <v>1712727855</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2289,10 +2350,11 @@
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Balcony.Temperature.state: Cold</t>
+          <t>Balcony.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2311,7 +2373,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1710544239</v>
+        <v>1712738524</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2321,10 +2383,11 @@
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Balcony.Temperature.state: Comfortable</t>
+          <t>Balcony.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2343,7 +2406,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1710556423</v>
+        <v>1712747911</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2357,6 +2420,7 @@
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2375,7 +2439,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1710605005</v>
+        <v>1712756443</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2389,6 +2453,7 @@
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2407,7 +2472,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1710619480</v>
+        <v>1712772373</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2421,6 +2486,7 @@
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2439,7 +2505,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1710632063</v>
+        <v>1712801114</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2453,6 +2519,7 @@
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2471,7 +2538,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1710639142</v>
+        <v>1712805626</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2485,6 +2552,7 @@
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2503,7 +2571,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1710668851</v>
+        <v>1712817686</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2513,10 +2581,11 @@
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Balcony.Temperature.state: Comfortable</t>
+          <t>Balcony.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2535,7 +2604,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1710705059</v>
+        <v>1712839240</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2545,10 +2614,11 @@
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Balcony.Temperature.state: Cold</t>
+          <t>Balcony.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2567,7 +2637,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1710715211</v>
+        <v>1712856862</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2581,6 +2651,7 @@
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2599,7 +2670,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1710727420</v>
+        <v>1712865358</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2609,10 +2680,11 @@
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Balcony.Temperature.state: Warm</t>
+          <t>Balcony.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2631,7 +2703,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1710738666</v>
+        <v>1712891245</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2641,10 +2713,11 @@
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Balcony.Temperature.state: ExcessivelyHot</t>
+          <t>Balcony.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2663,7 +2736,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1710745297</v>
+        <v>1712899825</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2677,6 +2750,7 @@
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2695,7 +2769,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1710751039</v>
+        <v>1712910704</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2705,10 +2779,11 @@
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Balcony.Temperature.state: Comfortable</t>
+          <t>Balcony.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2727,7 +2802,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1710756750</v>
+        <v>1712925230</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -2737,10 +2812,11 @@
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Balcony.Temperature.state: Cold</t>
+          <t>Balcony.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2759,7 +2835,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1710780261</v>
+        <v>1712939398</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -2773,6 +2849,7 @@
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2791,7 +2868,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1710786153</v>
+        <v>1712956699</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -2805,6 +2882,7 @@
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2823,7 +2901,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1710794720</v>
+        <v>1712984190</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -2837,6 +2915,7 @@
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2855,7 +2934,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1710809844</v>
+        <v>1712992638</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -2869,6 +2948,7 @@
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2887,7 +2967,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1710813690</v>
+        <v>1713016945</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -2897,10 +2977,11 @@
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Balcony.Temperature.state: ExcessivelyHot</t>
+          <t>Balcony.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2919,7 +3000,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1710827008</v>
+        <v>1713036872</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -2929,10 +3010,11 @@
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Balcony.Temperature.state: Warm</t>
+          <t>Balcony.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2951,7 +3033,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1710836183</v>
+        <v>1713064489</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -2965,6 +3047,7 @@
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2983,7 +3066,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1710842396</v>
+        <v>1713073038</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -2993,10 +3076,11 @@
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Balcony.Temperature.state: Cold</t>
+          <t>Balcony.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3015,7 +3099,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1710866680</v>
+        <v>1713082605</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -3025,10 +3109,11 @@
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Balcony.Temperature.state: Comfortable</t>
+          <t>Balcony.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3047,7 +3132,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1710871425</v>
+        <v>1713098572</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3057,10 +3142,11 @@
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Balcony.Temperature.state: Cold</t>
+          <t>Balcony.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3079,7 +3165,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1710882234</v>
+        <v>1713108186</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -3093,6 +3179,7 @@
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3111,7 +3198,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1710893738</v>
+        <v>1713127695</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3121,10 +3208,11 @@
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Balcony.Temperature.state: Warm</t>
+          <t>Balcony.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3143,7 +3231,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1710919444</v>
+        <v>1713156589</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3157,6 +3245,7 @@
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3175,7 +3264,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1710925103</v>
+        <v>1713165159</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3185,10 +3274,11 @@
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Balcony.Temperature.state: Cold</t>
+          <t>Balcony.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3207,7 +3297,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1710935218</v>
+        <v>1713181900</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3221,6 +3311,7 @@
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3239,7 +3330,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1710958711</v>
+        <v>1713242216</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3249,10 +3340,11 @@
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Balcony.Temperature.state: Cold</t>
+          <t>Balcony.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3271,7 +3363,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1710968299</v>
+        <v>1713250844</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3281,10 +3373,11 @@
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Balcony.Temperature.state: Comfortable</t>
+          <t>Balcony.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3303,7 +3396,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1710982219</v>
+        <v>1713274337</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3317,6 +3410,7 @@
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3335,7 +3429,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1711007940</v>
+        <v>1713283278</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -3349,6 +3443,7 @@
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3367,7 +3462,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1711012668</v>
+        <v>1713296799</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3381,6 +3476,7 @@
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3399,7 +3495,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1711050706</v>
+        <v>1713324759</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3413,6 +3509,7 @@
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3431,7 +3528,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>1711068189</v>
+        <v>1713333488</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -3445,6 +3542,7 @@
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3463,7 +3561,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>1711072242</v>
+        <v>1713344204</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3477,6 +3575,7 @@
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3495,7 +3594,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1711077323</v>
+        <v>1713357014</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -3509,6 +3608,7 @@
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3527,7 +3627,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>1711095590</v>
+        <v>1713373662</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -3541,6 +3641,7 @@
         </is>
       </c>
       <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3559,7 +3660,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>1711099251</v>
+        <v>1713387829</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -3573,6 +3674,7 @@
         </is>
       </c>
       <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3591,7 +3693,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1711144608</v>
+        <v>1713415921</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3605,6 +3707,7 @@
         </is>
       </c>
       <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3623,7 +3726,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1711154920</v>
+        <v>1713424605</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -3637,6 +3740,7 @@
         </is>
       </c>
       <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3655,7 +3759,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>1711158672</v>
+        <v>1713446947</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -3665,10 +3769,11 @@
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Balcony.Temperature.state: ExcessivelyHot</t>
+          <t>Balcony.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3687,7 +3792,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1711169914</v>
+        <v>1713470266</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -3697,10 +3802,11 @@
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Balcony.Temperature.state: Warm</t>
+          <t>Balcony.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3719,7 +3825,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>1711179948</v>
+        <v>1713496909</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -3733,6 +3839,7 @@
         </is>
       </c>
       <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3751,7 +3858,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>1711184690</v>
+        <v>1713505626</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -3761,10 +3868,11 @@
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Balcony.Temperature.state: Cold</t>
+          <t>Balcony.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3783,7 +3891,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1711211103</v>
+        <v>1713515205</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -3793,10 +3901,11 @@
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Balcony.Temperature.state: Comfortable</t>
+          <t>Balcony.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3815,7 +3924,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1711218141</v>
+        <v>1713530274</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -3825,10 +3934,11 @@
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Balcony.Temperature.state: Cold</t>
+          <t>Balcony.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3847,7 +3957,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>1711228020</v>
+        <v>1713538746</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -3861,6 +3971,7 @@
         </is>
       </c>
       <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3879,7 +3990,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>1711243679</v>
+        <v>1713556660</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -3889,10 +4000,11 @@
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Balcony.Temperature.state: Warm</t>
+          <t>Balcony.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3911,7 +4023,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>1711247380</v>
+        <v>1713584709</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -3921,10 +4033,11 @@
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Balcony.Temperature.state: ExcessivelyHot</t>
+          <t>Balcony.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3943,7 +4056,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1711252646</v>
+        <v>1713593013</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -3957,6 +4070,7 @@
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3975,7 +4089,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>1711258950</v>
+        <v>1713604324</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -3989,6 +4103,7 @@
         </is>
       </c>
       <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4007,7 +4122,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>1711264787</v>
+        <v>1713620176</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -4021,6 +4136,7 @@
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4039,7 +4155,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>1711272233</v>
+        <v>1713629306</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -4053,6 +4169,7 @@
         </is>
       </c>
       <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4071,7 +4188,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>1711278940</v>
+        <v>1713642236</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -4085,6 +4202,7 @@
         </is>
       </c>
       <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4103,7 +4221,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1711310533</v>
+        <v>1713668558</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -4117,6 +4235,7 @@
         </is>
       </c>
       <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4135,7 +4254,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1711328730</v>
+        <v>1713677217</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -4149,6 +4268,7 @@
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4167,7 +4287,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>1711332666</v>
+        <v>1713685822</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -4181,6 +4301,7 @@
         </is>
       </c>
       <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4199,7 +4320,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>1711338771</v>
+        <v>1713699816</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -4213,6 +4334,7 @@
         </is>
       </c>
       <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4231,7 +4353,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>1711358991</v>
+        <v>1713708411</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -4245,6 +4367,7 @@
         </is>
       </c>
       <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4263,7 +4386,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>1711361655</v>
+        <v>1713728326</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -4277,6 +4400,7 @@
         </is>
       </c>
       <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4295,7 +4419,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>1711364649</v>
+        <v>1713754831</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -4309,6 +4433,7 @@
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4327,7 +4452,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>1711389103</v>
+        <v>1713763600</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -4337,10 +4462,11 @@
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Balcony.Temperature.state: Cold</t>
+          <t>Balcony.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4359,7 +4485,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>1711394938</v>
+        <v>1713773750</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -4369,10 +4495,11 @@
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Balcony.Temperature.state: Comfortable</t>
+          <t>Balcony.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4391,7 +4518,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>1711419587</v>
+        <v>1713786604</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -4405,6 +4532,7 @@
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4423,7 +4551,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1711424190</v>
+        <v>1713795087</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -4433,10 +4561,11 @@
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Balcony.Temperature.state: ExcessivelyHot</t>
+          <t>Balcony.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4455,7 +4584,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>1711443638</v>
+        <v>1713814507</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -4465,10 +4594,11 @@
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Balcony.Temperature.state: Warm</t>
+          <t>Balcony.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4487,7 +4617,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>1711452876</v>
+        <v>1713841834</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -4501,6 +4631,7 @@
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4519,7 +4650,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>1711461792</v>
+        <v>1713850439</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -4529,10 +4660,11 @@
       <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Balcony.Temperature.state: Cold</t>
+          <t>Balcony.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4551,7 +4683,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>1711466793</v>
+        <v>1713861325</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -4561,10 +4693,11 @@
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Balcony.Temperature.state: Comfortable</t>
+          <t>Balcony.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4583,7 +4716,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>1711475547</v>
+        <v>1713874796</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -4593,10 +4726,11 @@
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Balcony.Temperature.state: Cold</t>
+          <t>Balcony.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4615,7 +4749,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>1711481530</v>
+        <v>1713889035</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -4629,6 +4763,7 @@
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4647,7 +4782,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>1711506714</v>
+        <v>1713905639</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -4657,10 +4792,11 @@
       <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Balcony.Temperature.state: Warm</t>
+          <t>Balcony.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4679,7 +4815,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>1711509117</v>
+        <v>1713933997</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -4693,6 +4829,7 @@
         </is>
       </c>
       <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4711,7 +4848,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>1711511529</v>
+        <v>1713942509</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -4725,6 +4862,7 @@
         </is>
       </c>
       <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4743,7 +4881,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>1711516025</v>
+        <v>1713965828</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -4757,6 +4895,7 @@
         </is>
       </c>
       <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4775,7 +4914,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>1711525995</v>
+        <v>1713992267</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -4785,10 +4924,11 @@
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Balcony.Temperature.state: Warm</t>
+          <t>Balcony.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4807,7 +4947,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>1711534042</v>
+        <v>1714020687</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -4821,6 +4961,7 @@
         </is>
       </c>
       <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4839,7 +4980,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>1711547068</v>
+        <v>1714029352</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -4849,10 +4990,11 @@
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Balcony.Temperature.state: Cold</t>
+          <t>Balcony.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4871,7 +5013,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>1711554853</v>
+        <v>1714053179</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -4885,6 +5027,7 @@
         </is>
       </c>
       <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4903,7 +5046,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>1711562562</v>
+        <v>1714073744</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -4917,6 +5060,7 @@
         </is>
       </c>
       <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4935,7 +5079,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>1711568874</v>
+        <v>1714101731</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -4949,6 +5093,7 @@
         </is>
       </c>
       <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4967,7 +5112,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>1711592358</v>
+        <v>1714110259</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -4981,6 +5126,7 @@
         </is>
       </c>
       <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4999,7 +5145,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>1711600867</v>
+        <v>1714121352</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -5009,10 +5155,11 @@
       <c r="F143" t="inlineStr"/>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Balcony.Temperature.state: Comfortable</t>
+          <t>Balcony.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5031,7 +5178,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>1711611096</v>
+        <v>1714132829</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -5045,6 +5192,7 @@
         </is>
       </c>
       <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5063,7 +5211,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>1711618501</v>
+        <v>1714144612</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -5077,6 +5225,7 @@
         </is>
       </c>
       <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5095,7 +5244,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>1711633583</v>
+        <v>1714159997</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -5109,6 +5258,7 @@
         </is>
       </c>
       <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5127,7 +5277,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>1711640050</v>
+        <v>1714187954</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -5141,6 +5291,337 @@
         </is>
       </c>
       <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Balcony</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>1714196306</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Balcony.Temperature.state: Warm</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Balcony</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>1714208027</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Balcony.Temperature.state: ExcessivelyHot</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Balcony</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>1714223198</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Balcony.Temperature.state: Warm</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Balcony</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>1714232223</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Balcony.Temperature.state: Comfortable</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Balcony</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>1714247408</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Balcony.Temperature.state: Cold</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Balcony</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>1714275815</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Balcony.Temperature.state: Comfortable</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Balcony</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>1714284214</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Balcony.Temperature.state: Warm</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Balcony</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>1714294203</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Balcony.Temperature.state: ExcessivelyHot</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Balcony</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>1714310233</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Balcony.Temperature.state: Warm</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Balcony</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>1714320147</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Balcony.Temperature.state: Comfortable</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
